--- a/wood-shell-tongue-drum-design-table.xlsx
+++ b/wood-shell-tongue-drum-design-table.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="31920" tabRatio="600" firstSheet="41" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="31920" tabRatio="600" firstSheet="41" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wood Shell Tongue Drum" sheetId="1" state="visible" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <numFmt numFmtId="184" formatCode="0.000&quot;&quot;"/>
     <numFmt numFmtId="185" formatCode="0.0&quot;&quot;"/>
   </numFmts>
-  <fonts count="90">
+  <fonts count="95">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -556,8 +556,27 @@
       <color rgb="FF000000"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F1922"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="003F4A55"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <color rgb="000000FF"/>
+    </font>
   </fonts>
-  <fills count="90">
+  <fills count="93">
     <fill>
       <patternFill/>
     </fill>
@@ -1092,8 +1111,23 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EDF2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF1F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="62">
+  <borders count="67">
     <border>
       <left/>
       <right/>
@@ -1822,12 +1856,70 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="009AA5B1"/>
+      </left>
+      <right style="thin">
+        <color rgb="009AA5B1"/>
+      </right>
+      <top style="thin">
+        <color rgb="009AA5B1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009AA5B1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009AA5B1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009AA5B1"/>
+      </right>
+      <top style="thin">
+        <color rgb="009AA5B1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009AA5B1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009AA5B1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009AA5B1"/>
+      </right>
+      <top style="thin">
+        <color rgb="009AA5B1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009AA5B1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="19" fillId="0" borderId="26"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="26"/>
   </cellStyleXfs>
-  <cellXfs count="850">
+  <cellXfs count="868">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3243,6 +3335,54 @@
     </xf>
     <xf numFmtId="0" fontId="85" fillId="88" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="90" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="94" fillId="91" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="94" fillId="91" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="91" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="92" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3724,12 +3864,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I171"/>
+  <dimension ref="A1:I284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="137.140625" customWidth="1" style="817" min="1" max="1"/>
-    <col width="34.28515625" customWidth="1" style="817" min="2" max="2"/>
-    <col width="22.85546875" customWidth="1" style="817" min="3" max="5"/>
+    <col width="32" customWidth="1" style="817" min="1" max="1"/>
+    <col width="18" customWidth="1" style="817" min="2" max="2"/>
+    <col width="18" customWidth="1" style="817" min="3" max="5"/>
+    <col width="18" customWidth="1" style="817" min="4" max="4"/>
+    <col width="60" customWidth="1" style="817" min="5" max="5"/>
     <col width="19" customWidth="1" style="817" min="6" max="7"/>
     <col width="15.28515625" customWidth="1" style="817" min="8" max="8"/>
     <col width="19" customWidth="1" style="817" min="9" max="9"/>
@@ -5856,7 +5998,2003 @@
         </is>
       </c>
     </row>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175">
+      <c r="A175" s="850" t="inlineStr">
+        <is>
+          <t>ROUND-BODY VARIANT MATRIX — Cylinder × Hemisphere × Flat × Dome × Three Sizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="851" t="inlineStr">
+        <is>
+          <t>Extends Concepts A/B/C above with explicit round-body design candidates. Four geometric variants × three size presets = 12 design candidates. Each variant carries its own chamber-volume formula, Helmholtz coupling, and tongue-fit verdict. All values are formulas tied to the SIZE PRESETS block below — change a preset cell and the entire matrix updates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177"/>
+    <row r="178">
+      <c r="A178" s="850" t="inlineStr">
+        <is>
+          <t>§B. SIZE PRESETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="852" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B179" s="852" t="inlineStr">
+        <is>
+          <t>Travel (12")</t>
+        </is>
+      </c>
+      <c r="C179" s="852" t="inlineStr">
+        <is>
+          <t>Standard (16")</t>
+        </is>
+      </c>
+      <c r="D179" s="852" t="inlineStr">
+        <is>
+          <t>Floor Pouf (20")</t>
+        </is>
+      </c>
+      <c r="E179" s="852" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="853" t="inlineStr">
+        <is>
+          <t>Outer Diameter (in)</t>
+        </is>
+      </c>
+      <c r="B180" s="854" t="n">
+        <v>12</v>
+      </c>
+      <c r="C180" s="854" t="n">
+        <v>16</v>
+      </c>
+      <c r="D180" s="854" t="n">
+        <v>20</v>
+      </c>
+      <c r="E180" s="855" t="inlineStr">
+        <is>
+          <t>Travel matches steel-pan size; Standard ≈ Moroccan ottoman; Floor Pouf ≈ tall lounge piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="853" t="inlineStr">
+        <is>
+          <t>Shell Height (in)</t>
+        </is>
+      </c>
+      <c r="B181" s="854" t="n">
+        <v>5</v>
+      </c>
+      <c r="C181" s="854" t="n">
+        <v>8</v>
+      </c>
+      <c r="D181" s="854" t="n">
+        <v>10</v>
+      </c>
+      <c r="E181" s="855" t="inlineStr">
+        <is>
+          <t>Cylinder body height (rim to floor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="853" t="inlineStr">
+        <is>
+          <t>Soundboard Thickness (in)</t>
+        </is>
+      </c>
+      <c r="B182" s="856" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C182" s="856" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D182" s="856" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E182" s="855" t="inlineStr">
+        <is>
+          <t>Travel 12 in uses 1/4 in for fit; Standard 16 in 3/8 in; Floor Pouf 20 in 1/2 in for stiffness across span</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="853" t="inlineStr">
+        <is>
+          <t>Soundboard Wood</t>
+        </is>
+      </c>
+      <c r="B183" s="857" t="inlineStr">
+        <is>
+          <t>Padauk</t>
+        </is>
+      </c>
+      <c r="C183" s="857" t="inlineStr">
+        <is>
+          <t>Padauk</t>
+        </is>
+      </c>
+      <c r="D183" s="857" t="inlineStr">
+        <is>
+          <t>Padauk</t>
+        </is>
+      </c>
+      <c r="E183" s="855" t="inlineStr">
+        <is>
+          <t>Cedar (K≈29,013) shortens tongues — use on tight-fit configs</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="853" t="inlineStr">
+        <is>
+          <t>Cantilever K (from library)</t>
+        </is>
+      </c>
+      <c r="B184" s="854" t="n">
+        <v>24438</v>
+      </c>
+      <c r="C184" s="854" t="n">
+        <v>24438</v>
+      </c>
+      <c r="D184" s="854" t="n">
+        <v>24438</v>
+      </c>
+      <c r="E184" s="855" t="inlineStr">
+        <is>
+          <t>Padauk K = 24,438 (see library row 19). Update if wood changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="853" t="inlineStr">
+        <is>
+          <t>Slit Kerf Width (in)</t>
+        </is>
+      </c>
+      <c r="B185" s="856" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="C185" s="856" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D185" s="856" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="E185" s="855" t="inlineStr">
+        <is>
+          <t>1/8" CNC upcut spiral — same on all sizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="853" t="inlineStr">
+        <is>
+          <t>Tongue Width (in)</t>
+        </is>
+      </c>
+      <c r="B186" s="856" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186" s="856" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D186" s="856" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E186" s="855" t="inlineStr">
+        <is>
+          <t>Wider tongues = more volume; pitch unchanged</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="853" t="inlineStr">
+        <is>
+          <t>Number of Tongues</t>
+        </is>
+      </c>
+      <c r="B187" s="854" t="n">
+        <v>11</v>
+      </c>
+      <c r="C187" s="854" t="n">
+        <v>11</v>
+      </c>
+      <c r="D187" s="854" t="n">
+        <v>11</v>
+      </c>
+      <c r="E187" s="855" t="inlineStr">
+        <is>
+          <t>Standard 11-note (1 ding + 10 chromatic above) on all sizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="853" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="B188" s="857" t="inlineStr">
+        <is>
+          <t>D Kurd</t>
+        </is>
+      </c>
+      <c r="C188" s="857" t="inlineStr">
+        <is>
+          <t>A Kurd</t>
+        </is>
+      </c>
+      <c r="D188" s="857" t="inlineStr">
+        <is>
+          <t>D Kurd</t>
+        </is>
+      </c>
+      <c r="E188" s="855" t="inlineStr">
+        <is>
+          <t>Match scale to ding fitness — see Variant blocks below</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="853" t="inlineStr">
+        <is>
+          <t>Target Ding Note</t>
+        </is>
+      </c>
+      <c r="B189" s="857" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C189" s="857" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D189" s="857" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E189" s="855" t="inlineStr">
+        <is>
+          <t>Anchor pitch; 12" too small for D3 in wood</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="853" t="inlineStr">
+        <is>
+          <t>Ding MIDI #</t>
+        </is>
+      </c>
+      <c r="B190" s="854" t="n">
+        <v>62</v>
+      </c>
+      <c r="C190" s="854" t="n">
+        <v>57</v>
+      </c>
+      <c r="D190" s="854" t="n">
+        <v>50</v>
+      </c>
+      <c r="E190" s="855" t="inlineStr">
+        <is>
+          <t>D4=62, A3=57, D3=50</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="853" t="inlineStr">
+        <is>
+          <t>Ding Frequency (Hz)</t>
+        </is>
+      </c>
+      <c r="B191" s="858">
+        <f>440*2^((B190-69)/12)</f>
+        <v/>
+      </c>
+      <c r="C191" s="858">
+        <f>440*2^((C190-69)/12)</f>
+        <v/>
+      </c>
+      <c r="D191" s="858">
+        <f>440*2^((D190-69)/12)</f>
+        <v/>
+      </c>
+      <c r="E191" s="855" t="inlineStr">
+        <is>
+          <t>Computed from MIDI #</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="853" t="inlineStr">
+        <is>
+          <t>Bowl/Shell Wood</t>
+        </is>
+      </c>
+      <c r="B192" s="857" t="inlineStr">
+        <is>
+          <t>Black Walnut</t>
+        </is>
+      </c>
+      <c r="C192" s="857" t="inlineStr">
+        <is>
+          <t>Black Walnut</t>
+        </is>
+      </c>
+      <c r="D192" s="857" t="inlineStr">
+        <is>
+          <t>Black Walnut</t>
+        </is>
+      </c>
+      <c r="E192" s="855" t="inlineStr">
+        <is>
+          <t>Bowl is structural — pick attractive hardwood</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="853" t="inlineStr">
+        <is>
+          <t>Gu Port Diameter (in)</t>
+        </is>
+      </c>
+      <c r="B193" s="856" t="n">
+        <v>2</v>
+      </c>
+      <c r="C193" s="856" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D193" s="856" t="n">
+        <v>3</v>
+      </c>
+      <c r="E193" s="855" t="inlineStr">
+        <is>
+          <t>Bottom port. Larger Ø → higher Helmholtz freq; tune to lowest tongue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="853" t="inlineStr">
+        <is>
+          <t>Dome Rise (in, top variants)</t>
+        </is>
+      </c>
+      <c r="B194" s="856" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C194" s="856" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D194" s="856" t="n">
+        <v>1</v>
+      </c>
+      <c r="E194" s="855" t="inlineStr">
+        <is>
+          <t>Crown height for Variants 2 &amp; 4. ≈ 4–6% of diameter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="853" t="inlineStr">
+        <is>
+          <t>Min Tongue Length Cap (in)</t>
+        </is>
+      </c>
+      <c r="B195" s="859">
+        <f>B180/2-1</f>
+        <v/>
+      </c>
+      <c r="C195" s="859">
+        <f>C180/2-1</f>
+        <v/>
+      </c>
+      <c r="D195" s="859">
+        <f>D180/2-1</f>
+        <v/>
+      </c>
+      <c r="E195" s="855" t="inlineStr">
+        <is>
+          <t>Radial fit cap: radius − 1" Ding-area clearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="850" t="inlineStr">
+        <is>
+          <t>§C. VARIANT 1 — Ottoman Cylinder, Flat Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="851" t="inlineStr">
+        <is>
+          <t>Stave or segmented cylinder shell + flat tonewood disc soundboard glued/screwed to the rim. Closest to the existing rectangular-prism wood tongue drum but with a round footprint. The lowest piece-count and most predictable tuning of the four — recommended starting point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="860" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B199" s="860" t="inlineStr">
+        <is>
+          <t>Travel 12"</t>
+        </is>
+      </c>
+      <c r="C199" s="860" t="inlineStr">
+        <is>
+          <t>Standard 16"</t>
+        </is>
+      </c>
+      <c r="D199" s="860" t="inlineStr">
+        <is>
+          <t>Floor Pouf 20"</t>
+        </is>
+      </c>
+      <c r="E199" s="860" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="861" t="inlineStr">
+        <is>
+          <t>Chamber Volume (in³)</t>
+        </is>
+      </c>
+      <c r="B200" s="862">
+        <f>PI()*($B$180/2)^2*$B$181</f>
+        <v/>
+      </c>
+      <c r="C200" s="862">
+        <f>PI()*($C$180/2)^2*$C$181</f>
+        <v/>
+      </c>
+      <c r="D200" s="862">
+        <f>PI()*($D$180/2)^2*$D$181</f>
+        <v/>
+      </c>
+      <c r="E200" s="855" t="inlineStr">
+        <is>
+          <t>Volume of enclosed air column (drives Helmholtz pitch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="861" t="inlineStr">
+        <is>
+          <t>Port Area (in²)</t>
+        </is>
+      </c>
+      <c r="B201" s="858">
+        <f>PI()*($B$193/2)^2</f>
+        <v/>
+      </c>
+      <c r="C201" s="858">
+        <f>PI()*($C$193/2)^2</f>
+        <v/>
+      </c>
+      <c r="D201" s="858">
+        <f>PI()*($D$193/2)^2</f>
+        <v/>
+      </c>
+      <c r="E201" s="855" t="inlineStr">
+        <is>
+          <t>Bottom Gu port (=π·r²)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="861" t="inlineStr">
+        <is>
+          <t>Effective Neck Length (in)</t>
+        </is>
+      </c>
+      <c r="B202" s="859">
+        <f>$B$182</f>
+        <v/>
+      </c>
+      <c r="C202" s="859">
+        <f>$C$182</f>
+        <v/>
+      </c>
+      <c r="D202" s="859">
+        <f>$D$182</f>
+        <v/>
+      </c>
+      <c r="E202" s="855">
+        <f> Soundboard thickness (port pierces only the bowl floor)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="861" t="inlineStr">
+        <is>
+          <t>Helmholtz Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="B203" s="862">
+        <f>(13552/(2*PI()))*SQRT(B201/(B200*B202))</f>
+        <v/>
+      </c>
+      <c r="C203" s="862">
+        <f>(13552/(2*PI()))*SQRT(C201/(C200*C202))</f>
+        <v/>
+      </c>
+      <c r="D203" s="862">
+        <f>(13552/(2*PI()))*SQRT(D201/(D200*D202))</f>
+        <v/>
+      </c>
+      <c r="E203" s="855" t="inlineStr">
+        <is>
+          <t>Should fall AT or BELOW the lowest tongue freq for warm bass coupling</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="861" t="inlineStr">
+        <is>
+          <t>Lowest Tongue Freq (Ding, Hz)</t>
+        </is>
+      </c>
+      <c r="B204" s="862">
+        <f>$B$191</f>
+        <v/>
+      </c>
+      <c r="C204" s="862">
+        <f>$C$191</f>
+        <v/>
+      </c>
+      <c r="D204" s="862">
+        <f>$D$191</f>
+        <v/>
+      </c>
+      <c r="E204" s="855">
+        <f> ding freq from preset row</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="861" t="inlineStr">
+        <is>
+          <t>Helmholtz–Ding Coupling</t>
+        </is>
+      </c>
+      <c r="B205" s="863">
+        <f>IF(ABS(B203-B204)/B204&lt;=0.2,"Coupled (within 20%)",IF(B203&lt;B204,"Below ding (warm bass)","Above ding (mistuned)"))</f>
+        <v/>
+      </c>
+      <c r="C205" s="863">
+        <f>IF(ABS(C203-C204)/C204&lt;=0.2,"Coupled (within 20%)",IF(C203&lt;C204,"Below ding (warm bass)","Above ding (mistuned)"))</f>
+        <v/>
+      </c>
+      <c r="D205" s="863">
+        <f>IF(ABS(D203-D204)/D204&lt;=0.2,"Coupled (within 20%)",IF(D203&lt;D204,"Below ding (warm bass)","Above ding (mistuned)"))</f>
+        <v/>
+      </c>
+      <c r="E205" s="855" t="inlineStr">
+        <is>
+          <t>±20 % of ding = coupled regime; below ding = bass extension; above = mistuned</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="861" t="inlineStr">
+        <is>
+          <t>Ding Tongue Length (in)</t>
+        </is>
+      </c>
+      <c r="B206" s="858">
+        <f>SQRT($B$184*$B$182/$B$191)</f>
+        <v/>
+      </c>
+      <c r="C206" s="858">
+        <f>SQRT($C$184*$C$182/$C$191)</f>
+        <v/>
+      </c>
+      <c r="D206" s="858">
+        <f>SQRT($D$184*$D$182/$D$191)</f>
+        <v/>
+      </c>
+      <c r="E206" s="855" t="inlineStr">
+        <is>
+          <t>L = √(K·t/f), flat-cantilever Euler-Bernoulli</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="861" t="inlineStr">
+        <is>
+          <t>Fit Verdict</t>
+        </is>
+      </c>
+      <c r="B207" s="863">
+        <f>IF(B206&lt;=$B$195,"Fits OK",IF(B206&lt;=$B$195*1.1,"Tight (within 10%)","Wont fit"))</f>
+        <v/>
+      </c>
+      <c r="C207" s="863">
+        <f>IF(C206&lt;=$C$195,"Fits OK",IF(C206&lt;=$C$195*1.1,"Tight (within 10%)","Wont fit"))</f>
+        <v/>
+      </c>
+      <c r="D207" s="863">
+        <f>IF(D206&lt;=$D$195,"Fits OK",IF(D206&lt;=$D$195*1.1,"Tight (within 10%)","Wont fit"))</f>
+        <v/>
+      </c>
+      <c r="E207" s="855" t="inlineStr">
+        <is>
+          <t>Fits OK ≤ radial cap • Tight within 10% • Wont fit if exceeds shell radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="861" t="inlineStr">
+        <is>
+          <t>Top Construction</t>
+        </is>
+      </c>
+      <c r="B208" s="864" t="inlineStr">
+        <is>
+          <t>Flat tonewood disc (CNC-cut to OD, edge-rabbeted into shell rim). Slits routed before glue-up. Optional perimeter sound port for additional tuning. Disc dia = shell OD; thickness from preset.</t>
+        </is>
+      </c>
+      <c r="C208" s="865" t="n"/>
+      <c r="D208" s="865" t="n"/>
+      <c r="E208" s="866" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="861" t="inlineStr">
+        <is>
+          <t>Tongue Physics</t>
+        </is>
+      </c>
+      <c r="B209" s="864" t="inlineStr">
+        <is>
+          <t>Standard flat cantilever — formulas in row 38 onward apply directly. Empirical detuning &lt;= 1 % observed on rectangular drums; trust the model.</t>
+        </is>
+      </c>
+      <c r="C209" s="865" t="n"/>
+      <c r="D209" s="865" t="n"/>
+      <c r="E209" s="866" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="861" t="inlineStr">
+        <is>
+          <t>Risk / Difficulty</t>
+        </is>
+      </c>
+      <c r="B210" s="864" t="inlineStr">
+        <is>
+          <t>**  — Proven flat-cantilever physics + well-trodden stave/segmented bowl method. Lowest risk.</t>
+        </is>
+      </c>
+      <c r="C210" s="865" t="n"/>
+      <c r="D210" s="865" t="n"/>
+      <c r="E210" s="866" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="850" t="inlineStr">
+        <is>
+          <t>§D. VARIANT 2 — Ottoman Cylinder, Domed Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="851" t="inlineStr">
+        <is>
+          <t>Same cylinder body as Variant 1 but with a shallow CNC-domed soundboard (steel-tongue-drum silhouette in wood). Dome is glue-laminated thick blank, 3D-surfaced top + bottom on CNC, then laser-aligned tongue slits cut into the curved face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="860" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B214" s="860" t="inlineStr">
+        <is>
+          <t>Travel 12"</t>
+        </is>
+      </c>
+      <c r="C214" s="860" t="inlineStr">
+        <is>
+          <t>Standard 16"</t>
+        </is>
+      </c>
+      <c r="D214" s="860" t="inlineStr">
+        <is>
+          <t>Floor Pouf 20"</t>
+        </is>
+      </c>
+      <c r="E214" s="860" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="861" t="inlineStr">
+        <is>
+          <t>Chamber Volume (in³)</t>
+        </is>
+      </c>
+      <c r="B215" s="862">
+        <f>PI()*($B$180/2)^2*$B$181+(PI()*$B$194*(3*($B$180/2)^2+$B$194^2))/6</f>
+        <v/>
+      </c>
+      <c r="C215" s="862">
+        <f>PI()*($C$180/2)^2*$C$181+(PI()*$C$194*(3*($C$180/2)^2+$C$194^2))/6</f>
+        <v/>
+      </c>
+      <c r="D215" s="862">
+        <f>PI()*($D$180/2)^2*$D$181+(PI()*$D$194*(3*($D$180/2)^2+$D$194^2))/6</f>
+        <v/>
+      </c>
+      <c r="E215" s="855" t="inlineStr">
+        <is>
+          <t>Volume of enclosed air column (drives Helmholtz pitch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="861" t="inlineStr">
+        <is>
+          <t>Port Area (in²)</t>
+        </is>
+      </c>
+      <c r="B216" s="858">
+        <f>PI()*($B$193/2)^2</f>
+        <v/>
+      </c>
+      <c r="C216" s="858">
+        <f>PI()*($C$193/2)^2</f>
+        <v/>
+      </c>
+      <c r="D216" s="858">
+        <f>PI()*($D$193/2)^2</f>
+        <v/>
+      </c>
+      <c r="E216" s="855" t="inlineStr">
+        <is>
+          <t>Bottom Gu port (=π·r²)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="861" t="inlineStr">
+        <is>
+          <t>Effective Neck Length (in)</t>
+        </is>
+      </c>
+      <c r="B217" s="859">
+        <f>$B$182+0.5*$B$194</f>
+        <v/>
+      </c>
+      <c r="C217" s="859">
+        <f>$C$182+0.5*$C$194</f>
+        <v/>
+      </c>
+      <c r="D217" s="859">
+        <f>$D$182+0.5*$D$194</f>
+        <v/>
+      </c>
+      <c r="E217" s="855" t="inlineStr">
+        <is>
+          <t>Soundboard thickness + ½ dome rise (longer neck → lower Helmholtz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="861" t="inlineStr">
+        <is>
+          <t>Helmholtz Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="B218" s="862">
+        <f>(13552/(2*PI()))*SQRT(B216/(B215*B217))</f>
+        <v/>
+      </c>
+      <c r="C218" s="862">
+        <f>(13552/(2*PI()))*SQRT(C216/(C215*C217))</f>
+        <v/>
+      </c>
+      <c r="D218" s="862">
+        <f>(13552/(2*PI()))*SQRT(D216/(D215*D217))</f>
+        <v/>
+      </c>
+      <c r="E218" s="855" t="inlineStr">
+        <is>
+          <t>Should fall AT or BELOW the lowest tongue freq for warm bass coupling</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="861" t="inlineStr">
+        <is>
+          <t>Lowest Tongue Freq (Ding, Hz)</t>
+        </is>
+      </c>
+      <c r="B219" s="862">
+        <f>$B$191</f>
+        <v/>
+      </c>
+      <c r="C219" s="862">
+        <f>$C$191</f>
+        <v/>
+      </c>
+      <c r="D219" s="862">
+        <f>$D$191</f>
+        <v/>
+      </c>
+      <c r="E219" s="855">
+        <f> ding freq from preset row</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="861" t="inlineStr">
+        <is>
+          <t>Helmholtz–Ding Coupling</t>
+        </is>
+      </c>
+      <c r="B220" s="863">
+        <f>IF(ABS(B218-B219)/B219&lt;=0.2,"Coupled (within 20%)",IF(B218&lt;B219,"Below ding (warm bass)","Above ding (mistuned)"))</f>
+        <v/>
+      </c>
+      <c r="C220" s="863">
+        <f>IF(ABS(C218-C219)/C219&lt;=0.2,"Coupled (within 20%)",IF(C218&lt;C219,"Below ding (warm bass)","Above ding (mistuned)"))</f>
+        <v/>
+      </c>
+      <c r="D220" s="863">
+        <f>IF(ABS(D218-D219)/D219&lt;=0.2,"Coupled (within 20%)",IF(D218&lt;D219,"Below ding (warm bass)","Above ding (mistuned)"))</f>
+        <v/>
+      </c>
+      <c r="E220" s="855" t="inlineStr">
+        <is>
+          <t>±20 % of ding = coupled regime; below ding = bass extension; above = mistuned</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="861" t="inlineStr">
+        <is>
+          <t>Ding Tongue Length (in)</t>
+        </is>
+      </c>
+      <c r="B221" s="858">
+        <f>SQRT($B$184*$B$182/$B$191)*1.025</f>
+        <v/>
+      </c>
+      <c r="C221" s="858">
+        <f>SQRT($C$184*$C$182/$C$191)*1.025</f>
+        <v/>
+      </c>
+      <c r="D221" s="858">
+        <f>SQRT($D$184*$D$182/$D$191)*1.025</f>
+        <v/>
+      </c>
+      <c r="E221" s="855" t="inlineStr">
+        <is>
+          <t>L = √(K·t/f) × 1.025 (curvature adds ~2.5 % to length to match same pitch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="861" t="inlineStr">
+        <is>
+          <t>Fit Verdict</t>
+        </is>
+      </c>
+      <c r="B222" s="863">
+        <f>IF(B221&lt;=$B$195,"Fits OK",IF(B221&lt;=$B$195*1.1,"Tight (within 10%)","Wont fit"))</f>
+        <v/>
+      </c>
+      <c r="C222" s="863">
+        <f>IF(C221&lt;=$C$195,"Fits OK",IF(C221&lt;=$C$195*1.1,"Tight (within 10%)","Wont fit"))</f>
+        <v/>
+      </c>
+      <c r="D222" s="863">
+        <f>IF(D221&lt;=$D$195,"Fits OK",IF(D221&lt;=$D$195*1.1,"Tight (within 10%)","Wont fit"))</f>
+        <v/>
+      </c>
+      <c r="E222" s="855" t="inlineStr">
+        <is>
+          <t>Fits OK ≤ radial cap • Tight within 10% • Wont fit if exceeds shell radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="861" t="inlineStr">
+        <is>
+          <t>Top Construction</t>
+        </is>
+      </c>
+      <c r="B223" s="864" t="inlineStr">
+        <is>
+          <t>Glue-up blank (3 plies x ~0.5") flatten, then 3D surface a parabolic dome (rise = preset). Bottom contour matches OD rim. Tongue slits: 1/8" upcut on a B-axis sled OR flatten the dome face on a fixture before slit routing.</t>
+        </is>
+      </c>
+      <c r="C223" s="865" t="n"/>
+      <c r="D223" s="865" t="n"/>
+      <c r="E223" s="866" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="861" t="inlineStr">
+        <is>
+          <t>Tongue Physics</t>
+        </is>
+      </c>
+      <c r="B224" s="864" t="inlineStr">
+        <is>
+          <t>Curved cantilever stiffer than flat — apply +2.5 % length correction (built into the Ding Tongue Length formula above). Validate empirically: tap-tune one tongue and back-fit the multiplier before cutting all 11.</t>
+        </is>
+      </c>
+      <c r="C224" s="865" t="n"/>
+      <c r="D224" s="865" t="n"/>
+      <c r="E224" s="866" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="861" t="inlineStr">
+        <is>
+          <t>Risk / Difficulty</t>
+        </is>
+      </c>
+      <c r="B225" s="864" t="inlineStr">
+        <is>
+          <t>*** — Adds dome-surfacing risk. Prototype the dome in poplar before committing to Padauk.</t>
+        </is>
+      </c>
+      <c r="C225" s="865" t="n"/>
+      <c r="D225" s="865" t="n"/>
+      <c r="E225" s="866" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="850" t="inlineStr">
+        <is>
+          <t>§E. VARIANT 3 — Hemisphere Bowl, Flat Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="851" t="inlineStr">
+        <is>
+          <t>True bowl-shaped shell — segmented (ring-stack) or thick-glue-up CNC-carved hemisphere — capped with a flat tonewood disc. Tagine / Moroccan-pouf silhouette. Bowl acts as a parabolic reflector, projecting tongue energy upward and outward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="860" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B229" s="860" t="inlineStr">
+        <is>
+          <t>Travel 12"</t>
+        </is>
+      </c>
+      <c r="C229" s="860" t="inlineStr">
+        <is>
+          <t>Standard 16"</t>
+        </is>
+      </c>
+      <c r="D229" s="860" t="inlineStr">
+        <is>
+          <t>Floor Pouf 20"</t>
+        </is>
+      </c>
+      <c r="E229" s="860" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="861" t="inlineStr">
+        <is>
+          <t>Chamber Volume (in³)</t>
+        </is>
+      </c>
+      <c r="B230" s="862">
+        <f>(PI()*$B$181^2*(3*(($B$181^2+($B$180/2)^2)/(2*$B$181))-$B$181))/3</f>
+        <v/>
+      </c>
+      <c r="C230" s="862">
+        <f>(PI()*$C$181^2*(3*(($C$181^2+($C$180/2)^2)/(2*$C$181))-$C$181))/3</f>
+        <v/>
+      </c>
+      <c r="D230" s="862">
+        <f>(PI()*$D$181^2*(3*(($D$181^2+($D$180/2)^2)/(2*$D$181))-$D$181))/3</f>
+        <v/>
+      </c>
+      <c r="E230" s="855" t="inlineStr">
+        <is>
+          <t>Volume of enclosed air column (drives Helmholtz pitch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="861" t="inlineStr">
+        <is>
+          <t>Port Area (in²)</t>
+        </is>
+      </c>
+      <c r="B231" s="858">
+        <f>PI()*($B$193/2)^2</f>
+        <v/>
+      </c>
+      <c r="C231" s="858">
+        <f>PI()*($C$193/2)^2</f>
+        <v/>
+      </c>
+      <c r="D231" s="858">
+        <f>PI()*($D$193/2)^2</f>
+        <v/>
+      </c>
+      <c r="E231" s="855" t="inlineStr">
+        <is>
+          <t>Bottom Gu port (=π·r²)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="861" t="inlineStr">
+        <is>
+          <t>Effective Neck Length (in)</t>
+        </is>
+      </c>
+      <c r="B232" s="859">
+        <f>$B$182</f>
+        <v/>
+      </c>
+      <c r="C232" s="859">
+        <f>$C$182</f>
+        <v/>
+      </c>
+      <c r="D232" s="859">
+        <f>$D$182</f>
+        <v/>
+      </c>
+      <c r="E232" s="855">
+        <f> Soundboard thickness (port pierces only the bowl floor)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="861" t="inlineStr">
+        <is>
+          <t>Helmholtz Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="B233" s="862">
+        <f>(13552/(2*PI()))*SQRT(B231/(B230*B232))</f>
+        <v/>
+      </c>
+      <c r="C233" s="862">
+        <f>(13552/(2*PI()))*SQRT(C231/(C230*C232))</f>
+        <v/>
+      </c>
+      <c r="D233" s="862">
+        <f>(13552/(2*PI()))*SQRT(D231/(D230*D232))</f>
+        <v/>
+      </c>
+      <c r="E233" s="855" t="inlineStr">
+        <is>
+          <t>Should fall AT or BELOW the lowest tongue freq for warm bass coupling</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="861" t="inlineStr">
+        <is>
+          <t>Lowest Tongue Freq (Ding, Hz)</t>
+        </is>
+      </c>
+      <c r="B234" s="862">
+        <f>$B$191</f>
+        <v/>
+      </c>
+      <c r="C234" s="862">
+        <f>$C$191</f>
+        <v/>
+      </c>
+      <c r="D234" s="862">
+        <f>$D$191</f>
+        <v/>
+      </c>
+      <c r="E234" s="855">
+        <f> ding freq from preset row</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="861" t="inlineStr">
+        <is>
+          <t>Helmholtz–Ding Coupling</t>
+        </is>
+      </c>
+      <c r="B235" s="863">
+        <f>IF(ABS(B233-B234)/B234&lt;=0.2,"Coupled (within 20%)",IF(B233&lt;B234,"Below ding (warm bass)","Above ding (mistuned)"))</f>
+        <v/>
+      </c>
+      <c r="C235" s="863">
+        <f>IF(ABS(C233-C234)/C234&lt;=0.2,"Coupled (within 20%)",IF(C233&lt;C234,"Below ding (warm bass)","Above ding (mistuned)"))</f>
+        <v/>
+      </c>
+      <c r="D235" s="863">
+        <f>IF(ABS(D233-D234)/D234&lt;=0.2,"Coupled (within 20%)",IF(D233&lt;D234,"Below ding (warm bass)","Above ding (mistuned)"))</f>
+        <v/>
+      </c>
+      <c r="E235" s="855" t="inlineStr">
+        <is>
+          <t>±20 % of ding = coupled regime; below ding = bass extension; above = mistuned</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="861" t="inlineStr">
+        <is>
+          <t>Ding Tongue Length (in)</t>
+        </is>
+      </c>
+      <c r="B236" s="858">
+        <f>SQRT($B$184*$B$182/$B$191)</f>
+        <v/>
+      </c>
+      <c r="C236" s="858">
+        <f>SQRT($C$184*$C$182/$C$191)</f>
+        <v/>
+      </c>
+      <c r="D236" s="858">
+        <f>SQRT($D$184*$D$182/$D$191)</f>
+        <v/>
+      </c>
+      <c r="E236" s="855" t="inlineStr">
+        <is>
+          <t>L = √(K·t/f), flat-cantilever Euler-Bernoulli</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="861" t="inlineStr">
+        <is>
+          <t>Fit Verdict</t>
+        </is>
+      </c>
+      <c r="B237" s="863">
+        <f>IF(B236&lt;=$B$195,"Fits OK",IF(B236&lt;=$B$195*1.1,"Tight (within 10%)","Wont fit"))</f>
+        <v/>
+      </c>
+      <c r="C237" s="863">
+        <f>IF(C236&lt;=$C$195,"Fits OK",IF(C236&lt;=$C$195*1.1,"Tight (within 10%)","Wont fit"))</f>
+        <v/>
+      </c>
+      <c r="D237" s="863">
+        <f>IF(D236&lt;=$D$195,"Fits OK",IF(D236&lt;=$D$195*1.1,"Tight (within 10%)","Wont fit"))</f>
+        <v/>
+      </c>
+      <c r="E237" s="855" t="inlineStr">
+        <is>
+          <t>Fits OK ≤ radial cap • Tight within 10% • Wont fit if exceeds shell radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="861" t="inlineStr">
+        <is>
+          <t>Top Construction</t>
+        </is>
+      </c>
+      <c r="B238" s="864" t="inlineStr">
+        <is>
+          <t>Flat soundboard disc (same as Variant 1). Critical: shell rim must be precisely circular and planar — turn rim true on lathe AFTER segment glue-up. Rabbet for board is 0.25" deep.</t>
+        </is>
+      </c>
+      <c r="C238" s="865" t="n"/>
+      <c r="D238" s="865" t="n"/>
+      <c r="E238" s="866" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="861" t="inlineStr">
+        <is>
+          <t>Tongue Physics</t>
+        </is>
+      </c>
+      <c r="B239" s="864" t="inlineStr">
+        <is>
+          <t>Same flat cantilever as Variant 1. The bowl doesn't affect tongue physics, only the Helmholtz coupling and projection pattern.</t>
+        </is>
+      </c>
+      <c r="C239" s="865" t="n"/>
+      <c r="D239" s="865" t="n"/>
+      <c r="E239" s="866" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="861" t="inlineStr">
+        <is>
+          <t>Risk / Difficulty</t>
+        </is>
+      </c>
+      <c r="B240" s="864" t="inlineStr">
+        <is>
+          <t>**  — Bowl turning is straightforward at 12-16"; &gt;18" needs a lathe with &gt;=10" swing over bed.</t>
+        </is>
+      </c>
+      <c r="C240" s="865" t="n"/>
+      <c r="D240" s="865" t="n"/>
+      <c r="E240" s="866" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="850" t="inlineStr">
+        <is>
+          <t>§F. VARIANT 4 — Hemisphere Bowl, Domed Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="851" t="inlineStr">
+        <is>
+          <t>Most steel-tongue-drum-adjacent silhouette in wood: round bowl below + shallow dome above. Total profile reads as a near-sphere. Construction is the union of Variants 2 + 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="860" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B244" s="860" t="inlineStr">
+        <is>
+          <t>Travel 12"</t>
+        </is>
+      </c>
+      <c r="C244" s="860" t="inlineStr">
+        <is>
+          <t>Standard 16"</t>
+        </is>
+      </c>
+      <c r="D244" s="860" t="inlineStr">
+        <is>
+          <t>Floor Pouf 20"</t>
+        </is>
+      </c>
+      <c r="E244" s="860" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="861" t="inlineStr">
+        <is>
+          <t>Chamber Volume (in³)</t>
+        </is>
+      </c>
+      <c r="B245" s="862">
+        <f>(PI()*$B$181^2*(3*(($B$181^2+($B$180/2)^2)/(2*$B$181))-$B$181))/3+(PI()*$B$194*(3*($B$180/2)^2+$B$194^2))/6</f>
+        <v/>
+      </c>
+      <c r="C245" s="862">
+        <f>(PI()*$C$181^2*(3*(($C$181^2+($C$180/2)^2)/(2*$C$181))-$C$181))/3+(PI()*$C$194*(3*($C$180/2)^2+$C$194^2))/6</f>
+        <v/>
+      </c>
+      <c r="D245" s="862">
+        <f>(PI()*$D$181^2*(3*(($D$181^2+($D$180/2)^2)/(2*$D$181))-$D$181))/3+(PI()*$D$194*(3*($D$180/2)^2+$D$194^2))/6</f>
+        <v/>
+      </c>
+      <c r="E245" s="855" t="inlineStr">
+        <is>
+          <t>Volume of enclosed air column (drives Helmholtz pitch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="861" t="inlineStr">
+        <is>
+          <t>Port Area (in²)</t>
+        </is>
+      </c>
+      <c r="B246" s="858">
+        <f>PI()*($B$193/2)^2</f>
+        <v/>
+      </c>
+      <c r="C246" s="858">
+        <f>PI()*($C$193/2)^2</f>
+        <v/>
+      </c>
+      <c r="D246" s="858">
+        <f>PI()*($D$193/2)^2</f>
+        <v/>
+      </c>
+      <c r="E246" s="855" t="inlineStr">
+        <is>
+          <t>Bottom Gu port (=π·r²)</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="861" t="inlineStr">
+        <is>
+          <t>Effective Neck Length (in)</t>
+        </is>
+      </c>
+      <c r="B247" s="859">
+        <f>$B$182+0.5*$B$194</f>
+        <v/>
+      </c>
+      <c r="C247" s="859">
+        <f>$C$182+0.5*$C$194</f>
+        <v/>
+      </c>
+      <c r="D247" s="859">
+        <f>$D$182+0.5*$D$194</f>
+        <v/>
+      </c>
+      <c r="E247" s="855" t="inlineStr">
+        <is>
+          <t>Soundboard thickness + ½ dome rise (longer neck → lower Helmholtz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="861" t="inlineStr">
+        <is>
+          <t>Helmholtz Freq (Hz)</t>
+        </is>
+      </c>
+      <c r="B248" s="862">
+        <f>(13552/(2*PI()))*SQRT(B246/(B245*B247))</f>
+        <v/>
+      </c>
+      <c r="C248" s="862">
+        <f>(13552/(2*PI()))*SQRT(C246/(C245*C247))</f>
+        <v/>
+      </c>
+      <c r="D248" s="862">
+        <f>(13552/(2*PI()))*SQRT(D246/(D245*D247))</f>
+        <v/>
+      </c>
+      <c r="E248" s="855" t="inlineStr">
+        <is>
+          <t>Should fall AT or BELOW the lowest tongue freq for warm bass coupling</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="861" t="inlineStr">
+        <is>
+          <t>Lowest Tongue Freq (Ding, Hz)</t>
+        </is>
+      </c>
+      <c r="B249" s="862">
+        <f>$B$191</f>
+        <v/>
+      </c>
+      <c r="C249" s="862">
+        <f>$C$191</f>
+        <v/>
+      </c>
+      <c r="D249" s="862">
+        <f>$D$191</f>
+        <v/>
+      </c>
+      <c r="E249" s="855">
+        <f> ding freq from preset row</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="861" t="inlineStr">
+        <is>
+          <t>Helmholtz–Ding Coupling</t>
+        </is>
+      </c>
+      <c r="B250" s="863">
+        <f>IF(ABS(B248-B249)/B249&lt;=0.2,"Coupled (within 20%)",IF(B248&lt;B249,"Below ding (warm bass)","Above ding (mistuned)"))</f>
+        <v/>
+      </c>
+      <c r="C250" s="863">
+        <f>IF(ABS(C248-C249)/C249&lt;=0.2,"Coupled (within 20%)",IF(C248&lt;C249,"Below ding (warm bass)","Above ding (mistuned)"))</f>
+        <v/>
+      </c>
+      <c r="D250" s="863">
+        <f>IF(ABS(D248-D249)/D249&lt;=0.2,"Coupled (within 20%)",IF(D248&lt;D249,"Below ding (warm bass)","Above ding (mistuned)"))</f>
+        <v/>
+      </c>
+      <c r="E250" s="855" t="inlineStr">
+        <is>
+          <t>±20 % of ding = coupled regime; below ding = bass extension; above = mistuned</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="861" t="inlineStr">
+        <is>
+          <t>Ding Tongue Length (in)</t>
+        </is>
+      </c>
+      <c r="B251" s="858">
+        <f>SQRT($B$184*$B$182/$B$191)*1.025</f>
+        <v/>
+      </c>
+      <c r="C251" s="858">
+        <f>SQRT($C$184*$C$182/$C$191)*1.025</f>
+        <v/>
+      </c>
+      <c r="D251" s="858">
+        <f>SQRT($D$184*$D$182/$D$191)*1.025</f>
+        <v/>
+      </c>
+      <c r="E251" s="855" t="inlineStr">
+        <is>
+          <t>L = √(K·t/f) × 1.025 (curvature adds ~2.5 % to length to match same pitch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="861" t="inlineStr">
+        <is>
+          <t>Fit Verdict</t>
+        </is>
+      </c>
+      <c r="B252" s="863">
+        <f>IF(B251&lt;=$B$195,"Fits OK",IF(B251&lt;=$B$195*1.1,"Tight (within 10%)","Wont fit"))</f>
+        <v/>
+      </c>
+      <c r="C252" s="863">
+        <f>IF(C251&lt;=$C$195,"Fits OK",IF(C251&lt;=$C$195*1.1,"Tight (within 10%)","Wont fit"))</f>
+        <v/>
+      </c>
+      <c r="D252" s="863">
+        <f>IF(D251&lt;=$D$195,"Fits OK",IF(D251&lt;=$D$195*1.1,"Tight (within 10%)","Wont fit"))</f>
+        <v/>
+      </c>
+      <c r="E252" s="855" t="inlineStr">
+        <is>
+          <t>Fits OK ≤ radial cap • Tight within 10% • Wont fit if exceeds shell radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="861" t="inlineStr">
+        <is>
+          <t>Top Construction</t>
+        </is>
+      </c>
+      <c r="B253" s="864" t="inlineStr">
+        <is>
+          <t>Glued bowl (segmented or stave) + glue-up dome blank, both 3D-surfaced on CNC. Half-lap or rabbet joinery at rim. Final assembly clamps with a custom radius caul.</t>
+        </is>
+      </c>
+      <c r="C253" s="865" t="n"/>
+      <c r="D253" s="865" t="n"/>
+      <c r="E253" s="866" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="861" t="inlineStr">
+        <is>
+          <t>Tongue Physics</t>
+        </is>
+      </c>
+      <c r="B254" s="864" t="inlineStr">
+        <is>
+          <t>Curved cantilever +2.5 % correction (same as Variant 2). The flat-&gt;curved physics shift is the dominant uncertainty; budget extra prototype tongues.</t>
+        </is>
+      </c>
+      <c r="C254" s="865" t="n"/>
+      <c r="D254" s="865" t="n"/>
+      <c r="E254" s="866" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="861" t="inlineStr">
+        <is>
+          <t>Risk / Difficulty</t>
+        </is>
+      </c>
+      <c r="B255" s="864" t="inlineStr">
+        <is>
+          <t>****  — Highest piece-count + highest empirical tuning risk. Most beautiful result; build last.</t>
+        </is>
+      </c>
+      <c r="C255" s="865" t="n"/>
+      <c r="D255" s="865" t="n"/>
+      <c r="E255" s="866" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="850" t="inlineStr">
+        <is>
+          <t>§G. COMPATIBILITY MATRIX — Variant x Size at-a-glance</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="851" t="inlineStr">
+        <is>
+          <t>Quick-look summary. Cells reference the Fit Verdict and Helmholtz-Ding Coupling computed in C-F above. Stale? Press F9 to recalc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="852" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="B259" s="852" t="inlineStr">
+        <is>
+          <t>Travel 12"</t>
+        </is>
+      </c>
+      <c r="C259" s="852" t="inlineStr">
+        <is>
+          <t>Standard 16"</t>
+        </is>
+      </c>
+      <c r="D259" s="852" t="inlineStr">
+        <is>
+          <t>Floor Pouf 20"</t>
+        </is>
+      </c>
+      <c r="E259" s="852" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="853" t="inlineStr">
+        <is>
+          <t>1 - Cylinder . Flat Top</t>
+        </is>
+      </c>
+      <c r="B260" s="863">
+        <f>B207&amp;" / "&amp;B205</f>
+        <v/>
+      </c>
+      <c r="C260" s="863">
+        <f>C207&amp;" / "&amp;C205</f>
+        <v/>
+      </c>
+      <c r="D260" s="863">
+        <f>D207&amp;" / "&amp;D205</f>
+        <v/>
+      </c>
+      <c r="E260" s="855" t="inlineStr">
+        <is>
+          <t>Start here. 16" is the sweet spot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="853" t="inlineStr">
+        <is>
+          <t>2 - Cylinder . Domed Top</t>
+        </is>
+      </c>
+      <c r="B261" s="863">
+        <f>B222&amp;" / "&amp;B220</f>
+        <v/>
+      </c>
+      <c r="C261" s="863">
+        <f>C222&amp;" / "&amp;C220</f>
+        <v/>
+      </c>
+      <c r="D261" s="863">
+        <f>D222&amp;" / "&amp;D220</f>
+        <v/>
+      </c>
+      <c r="E261" s="855" t="inlineStr">
+        <is>
+          <t>Do this 2nd - proves dome workflow on simple body.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="853" t="inlineStr">
+        <is>
+          <t>3 - Hemisphere . Flat Top</t>
+        </is>
+      </c>
+      <c r="B262" s="863">
+        <f>B237&amp;" / "&amp;B235</f>
+        <v/>
+      </c>
+      <c r="C262" s="863">
+        <f>C237&amp;" / "&amp;C235</f>
+        <v/>
+      </c>
+      <c r="D262" s="863">
+        <f>D237&amp;" / "&amp;D235</f>
+        <v/>
+      </c>
+      <c r="E262" s="855" t="inlineStr">
+        <is>
+          <t>Do this 3rd - proves bowl workflow with safe top.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="853" t="inlineStr">
+        <is>
+          <t>4 - Hemisphere . Domed Top</t>
+        </is>
+      </c>
+      <c r="B263" s="863">
+        <f>B252&amp;" / "&amp;B250</f>
+        <v/>
+      </c>
+      <c r="C263" s="863">
+        <f>C252&amp;" / "&amp;C250</f>
+        <v/>
+      </c>
+      <c r="D263" s="863">
+        <f>D252&amp;" / "&amp;D250</f>
+        <v/>
+      </c>
+      <c r="E263" s="855" t="inlineStr">
+        <is>
+          <t>Final form. Build only after Variants 2 and 3 succeed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="850" t="inlineStr">
+        <is>
+          <t>§H. CONSTRUCTION NOTES — Round-Body Specifics</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="38" customHeight="1" s="817">
+      <c r="A266" s="867" t="inlineStr">
+        <is>
+          <t>1. Cylinder shell - staves</t>
+        </is>
+      </c>
+      <c r="B266" s="864" t="inlineStr">
+        <is>
+          <t>16 staves at 11.25 deg miter (180/16). Rip from 4/4 stock; jointed edges; band-clamp glue-up around an MDF cylinder mold. Lathe-true the OD and ID after cure (&gt;=24 h). Wall thickness after turning: 5/8-3/4 in.</t>
+        </is>
+      </c>
+      <c r="C266" s="865" t="n"/>
+      <c r="D266" s="865" t="n"/>
+      <c r="E266" s="866" t="n"/>
+    </row>
+    <row r="267" ht="38" customHeight="1" s="817">
+      <c r="A267" s="867" t="inlineStr">
+        <is>
+          <t>2. Cylinder shell - segmented</t>
+        </is>
+      </c>
+      <c r="B267" s="864" t="inlineStr">
+        <is>
+          <t>8 rings x 12 segments (15 deg miter). Same approach as your Ashiko (29 rings x 16) but lower ring count for shallower bodies. Stack rings on lazy-susan jig for glue-up. Diamond pattern with Walnut + Maple + Cherry accents reads beautifully on Ottoman size.</t>
+        </is>
+      </c>
+      <c r="C267" s="865" t="n"/>
+      <c r="D267" s="865" t="n"/>
+      <c r="E267" s="866" t="n"/>
+    </row>
+    <row r="268" ht="38" customHeight="1" s="817">
+      <c r="A268" s="867" t="inlineStr">
+        <is>
+          <t>3. Hemisphere bowl - segmented</t>
+        </is>
+      </c>
+      <c r="B268" s="864" t="inlineStr">
+        <is>
+          <t>Stack rings of decreasing diameter to approximate the spherical curve, then turn true on the lathe. Ring count 6-10 depending on size. Outer profile: parabolic to within 1/16 in of true sphere - OK because lathe finishes it.</t>
+        </is>
+      </c>
+      <c r="C268" s="865" t="n"/>
+      <c r="D268" s="865" t="n"/>
+      <c r="E268" s="866" t="n"/>
+    </row>
+    <row r="269" ht="38" customHeight="1" s="817">
+      <c r="A269" s="867" t="inlineStr">
+        <is>
+          <t>4. Hemisphere bowl - CNC carved</t>
+        </is>
+      </c>
+      <c r="B269" s="864" t="inlineStr">
+        <is>
+          <t>Glue-up thick blank (e.g., 4x 1 in plies of Walnut), then 3D-surface inside and outside on CNC with 3/4 in ball-end bit. Faster than segmenting for one-offs but heavy material waste.</t>
+        </is>
+      </c>
+      <c r="C269" s="865" t="n"/>
+      <c r="D269" s="865" t="n"/>
+      <c r="E269" s="866" t="n"/>
+    </row>
+    <row r="270" ht="38" customHeight="1" s="817">
+      <c r="A270" s="867" t="inlineStr">
+        <is>
+          <t>5. Domed top - 3D surfacing</t>
+        </is>
+      </c>
+      <c r="B270" s="864" t="inlineStr">
+        <is>
+          <t>Glue-up disc blank to OD + 1 in. 3D-surface convex top (parabolic, rise per preset) and concave underside in a flip-jig. Stepover 0.05 in for &lt;=32 microinch surface finish. Tongue slits routed AFTER shaping, on a sacrificial fixture that supports the dome.</t>
+        </is>
+      </c>
+      <c r="C270" s="865" t="n"/>
+      <c r="D270" s="865" t="n"/>
+      <c r="E270" s="866" t="n"/>
+    </row>
+    <row r="271" ht="38" customHeight="1" s="817">
+      <c r="A271" s="867" t="inlineStr">
+        <is>
+          <t>6. Domed top - alternate (steam-bent)</t>
+        </is>
+      </c>
+      <c r="B271" s="864" t="inlineStr">
+        <is>
+          <t>For thinner Ø &lt;= 16 in domes, bend a 1/4 in board over a CNC-routed positive form. Less waste than glue-up, but harder to keep flat-grained Padauk from springing back. Validate with poplar first.</t>
+        </is>
+      </c>
+      <c r="C271" s="865" t="n"/>
+      <c r="D271" s="865" t="n"/>
+      <c r="E271" s="866" t="n"/>
+    </row>
+    <row r="272" ht="38" customHeight="1" s="817">
+      <c r="A272" s="867" t="inlineStr">
+        <is>
+          <t>7. Tongue layout - radial</t>
+        </is>
+      </c>
+      <c r="B272" s="864" t="inlineStr">
+        <is>
+          <t>Same zigzag-ascending pattern as a steel tongue drum: ding centered, then alternating sides radially outward in scale order. Slit tongue width 1 in (Travel) -&gt; 1.5 in (Floor Pouf). Do not exceed 50 % of soundboard area in slit kerfs (structural).</t>
+        </is>
+      </c>
+      <c r="C272" s="865" t="n"/>
+      <c r="D272" s="865" t="n"/>
+      <c r="E272" s="866" t="n"/>
+    </row>
+    <row r="273" ht="38" customHeight="1" s="817">
+      <c r="A273" s="867" t="inlineStr">
+        <is>
+          <t>8. Bowl-top joint</t>
+        </is>
+      </c>
+      <c r="B273" s="864" t="inlineStr">
+        <is>
+          <t>Critical airtight joint. Options: (a) rabbet 1/4 in deep x board-thickness wide on the rim, drop soundboard in flush with PVA + cauls; (b) lap joint with stepped board; (c) gasket of 1/16 in cork. (a) is the best balance of acoustics and reversibility.</t>
+        </is>
+      </c>
+      <c r="C273" s="865" t="n"/>
+      <c r="D273" s="865" t="n"/>
+      <c r="E273" s="866" t="n"/>
+    </row>
+    <row r="274" ht="38" customHeight="1" s="817">
+      <c r="A274" s="867" t="inlineStr">
+        <is>
+          <t>9. Gu port - sizing</t>
+        </is>
+      </c>
+      <c r="B274" s="864" t="inlineStr">
+        <is>
+          <t>Drill through thickest part of bowl floor. Fit with rubber O-ring liner like a Hapi drum. Port Ø is the primary Helmholtz tuning knob: enlarge for higher bass, shrink for lower.</t>
+        </is>
+      </c>
+      <c r="C274" s="865" t="n"/>
+      <c r="D274" s="865" t="n"/>
+      <c r="E274" s="866" t="n"/>
+    </row>
+    <row r="275" ht="38" customHeight="1" s="817">
+      <c r="A275" s="867" t="inlineStr">
+        <is>
+          <t>10. Domed-tongue empirical correction</t>
+        </is>
+      </c>
+      <c r="B275" s="864" t="inlineStr">
+        <is>
+          <t>Curved cantilever stiffness scales with arc curvature. The +2.5 % length factor in §D and §F is a starting estimate from cylinder-shell theory at small radii. Tap-test ONE tongue at design length, measure pitch (e.g. with Tone Generator app), back-solve actual factor, then apply to remaining 10 tongues.</t>
+        </is>
+      </c>
+      <c r="C275" s="865" t="n"/>
+      <c r="D275" s="865" t="n"/>
+      <c r="E275" s="866" t="n"/>
+    </row>
+    <row r="276" ht="38" customHeight="1" s="817">
+      <c r="A276" s="867" t="inlineStr">
+        <is>
+          <t>11. Weight budget</t>
+        </is>
+      </c>
+      <c r="B276" s="864" t="inlineStr">
+        <is>
+          <t>Travel 12 in: shell ~3 lb + soundboard ~1 lb = 4 lb. Standard 16 in: 6-7 lb. Floor Pouf 20 in: 10-12 lb. Add carry handle (rope through bowl) for Standard and above.</t>
+        </is>
+      </c>
+      <c r="C276" s="865" t="n"/>
+      <c r="D276" s="865" t="n"/>
+      <c r="E276" s="866" t="n"/>
+    </row>
+    <row r="277" ht="38" customHeight="1" s="817">
+      <c r="A277" s="867" t="inlineStr">
+        <is>
+          <t>12. Original-design caveat</t>
+        </is>
+      </c>
+      <c r="B277" s="864" t="inlineStr">
+        <is>
+          <t>No commercial wood tongue drums exist in this round-body x dome-top format at this design depth. Treat all four variants as prototype-then-validate before committing premium tonewood.</t>
+        </is>
+      </c>
+      <c r="C277" s="865" t="n"/>
+      <c r="D277" s="865" t="n"/>
+      <c r="E277" s="866" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="850" t="inlineStr">
+        <is>
+          <t>§I. RECOMMENDED BUILD SEQUENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="36" customHeight="1" s="817">
+      <c r="A280" s="867" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="B280" s="861" t="inlineStr">
+        <is>
+          <t>Phase 1 - Prove cylinder + flat top</t>
+        </is>
+      </c>
+      <c r="C280" s="864" t="inlineStr">
+        <is>
+          <t>Build Variant 1 at Standard 16 in first. Padauk 3/8 in soundboard, A Kurd, 11 tongues. Confirms shell construction, gu-port tuning, bowl-top joint, and Helmholtz coupling all in one go.</t>
+        </is>
+      </c>
+      <c r="D280" s="865" t="n"/>
+      <c r="E280" s="866" t="n"/>
+    </row>
+    <row r="281" ht="36" customHeight="1" s="817">
+      <c r="A281" s="867" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="B281" s="861" t="inlineStr">
+        <is>
+          <t>Phase 2 - Prove dome surfacing</t>
+        </is>
+      </c>
+      <c r="C281" s="864" t="inlineStr">
+        <is>
+          <t>Build Variant 2 at the same Standard 16 in with same scale. Reuse the Phase-1 cylinder shell - only the soundboard changes. Quantifies the curved-cantilever correction factor.</t>
+        </is>
+      </c>
+      <c r="D281" s="865" t="n"/>
+      <c r="E281" s="866" t="n"/>
+    </row>
+    <row r="282" ht="36" customHeight="1" s="817">
+      <c r="A282" s="867" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="B282" s="861" t="inlineStr">
+        <is>
+          <t>Phase 3 - Prove bowl construction</t>
+        </is>
+      </c>
+      <c r="C282" s="864" t="inlineStr">
+        <is>
+          <t>Build Variant 3 at Standard 16 in with a flat top. Now you know flat-top + bowl independently.</t>
+        </is>
+      </c>
+      <c r="D282" s="865" t="n"/>
+      <c r="E282" s="866" t="n"/>
+    </row>
+    <row r="283" ht="36" customHeight="1" s="817">
+      <c r="A283" s="867" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="B283" s="861" t="inlineStr">
+        <is>
+          <t>Phase 4 - Combine learnings</t>
+        </is>
+      </c>
+      <c r="C283" s="864" t="inlineStr">
+        <is>
+          <t>Build Variant 4 at the size you most want as a finished piece (Standard 16 in or Floor Pouf 20 in). Premium tonewoods, signature Heifer Zephyr finish.</t>
+        </is>
+      </c>
+      <c r="D283" s="865" t="n"/>
+      <c r="E283" s="866" t="n"/>
+    </row>
+    <row r="284" ht="36" customHeight="1" s="817">
+      <c r="A284" s="867" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B284" s="861" t="inlineStr">
+        <is>
+          <t>Phase 5 - Travel size</t>
+        </is>
+      </c>
+      <c r="C284" s="864" t="inlineStr">
+        <is>
+          <t>Once Phase 4 is dialled, scale Variant 1 (or your favourite) DOWN to 12 in Travel. Smallest size has tightest tongue-fit margins; build last when you know the formulas hold.</t>
+        </is>
+      </c>
+      <c r="D284" s="865" t="n"/>
+      <c r="E284" s="866" t="n"/>
+    </row>
   </sheetData>
+  <mergeCells count="44">
+    <mergeCell ref="A227:I227"/>
+    <mergeCell ref="B255:E255"/>
+    <mergeCell ref="A212:I212"/>
+    <mergeCell ref="B269:E269"/>
+    <mergeCell ref="A243:I243"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B254:E254"/>
+    <mergeCell ref="B266:E266"/>
+    <mergeCell ref="C282:E282"/>
+    <mergeCell ref="B275:E275"/>
+    <mergeCell ref="A198:I198"/>
+    <mergeCell ref="A175:I175"/>
+    <mergeCell ref="A213:I213"/>
+    <mergeCell ref="B268:E268"/>
+    <mergeCell ref="A242:I242"/>
+    <mergeCell ref="B277:E277"/>
+    <mergeCell ref="B224:E224"/>
+    <mergeCell ref="B271:E271"/>
+    <mergeCell ref="B209:E209"/>
+    <mergeCell ref="B208:E208"/>
+    <mergeCell ref="B273:E273"/>
+    <mergeCell ref="C283:E283"/>
+    <mergeCell ref="A265:I265"/>
+    <mergeCell ref="B223:E223"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B276:E276"/>
+    <mergeCell ref="B272:E272"/>
+    <mergeCell ref="B210:E210"/>
+    <mergeCell ref="A258:I258"/>
+    <mergeCell ref="A176:I176"/>
+    <mergeCell ref="B253:E253"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B225:E225"/>
+    <mergeCell ref="A257:I257"/>
+    <mergeCell ref="B274:E274"/>
+    <mergeCell ref="A279:I279"/>
+    <mergeCell ref="C284:E284"/>
+    <mergeCell ref="A178:I178"/>
+    <mergeCell ref="C281:E281"/>
+    <mergeCell ref="A197:I197"/>
+    <mergeCell ref="B267:E267"/>
+    <mergeCell ref="A228:I228"/>
+    <mergeCell ref="B270:E270"/>
+    <mergeCell ref="C280:E280"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
